--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>71.53553178526525</v>
+        <v>11.6245239151056</v>
       </c>
       <c r="D2" t="n">
-        <v>71.55286160696647</v>
+        <v>11.62734001113205</v>
       </c>
       <c r="E2" t="n">
-        <v>16.6757147657339</v>
+        <v>2.709803649431759</v>
       </c>
       <c r="F2" t="n">
-        <v>19.7618180239577</v>
+        <v>3.211295428893126</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>66.67641121580333</v>
+        <v>10.83491682256804</v>
       </c>
       <c r="D3" t="n">
-        <v>38.24836770903539</v>
+        <v>6.215359752718252</v>
       </c>
       <c r="E3" t="n">
-        <v>16.6757147657339</v>
+        <v>2.709803649431759</v>
       </c>
       <c r="F3" t="n">
-        <v>19.7618180239577</v>
+        <v>3.211295428893126</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>65.3714625340571</v>
+        <v>10.62286266178428</v>
       </c>
       <c r="D4" t="n">
-        <v>77.8029941790894</v>
+        <v>12.64298655410203</v>
       </c>
       <c r="E4" t="n">
-        <v>16.6757147657339</v>
+        <v>2.709803649431759</v>
       </c>
       <c r="F4" t="n">
-        <v>19.7618180239577</v>
+        <v>3.211295428893126</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.42629208767431</v>
+        <v>5.431772464247076</v>
       </c>
       <c r="D5" t="n">
-        <v>44.05475358065753</v>
+        <v>7.158897456856848</v>
       </c>
       <c r="E5" t="n">
-        <v>16.6757147657339</v>
+        <v>2.709803649431759</v>
       </c>
       <c r="F5" t="n">
-        <v>19.7618180239577</v>
+        <v>3.211295428893126</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.12818964940449</v>
+        <v>5.70833081802823</v>
       </c>
       <c r="D6" t="n">
-        <v>56.01349325570624</v>
+        <v>9.102192654052265</v>
       </c>
       <c r="E6" t="n">
-        <v>16.6757147657339</v>
+        <v>2.709803649431759</v>
       </c>
       <c r="F6" t="n">
-        <v>19.7618180239577</v>
+        <v>3.211295428893126</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.88178119007992</v>
+        <v>3.718289443387987</v>
       </c>
       <c r="D7" t="n">
-        <v>22.68792601518262</v>
+        <v>3.686787977467175</v>
       </c>
       <c r="E7" t="n">
-        <v>16.6757147657339</v>
+        <v>2.709803649431759</v>
       </c>
       <c r="F7" t="n">
-        <v>19.7618180239577</v>
+        <v>3.211295428893126</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.72355108163148</v>
+        <v>5.805077050765115</v>
       </c>
       <c r="D8" t="n">
-        <v>19.31320791582797</v>
+        <v>3.138396286322044</v>
       </c>
       <c r="E8" t="n">
-        <v>16.6757147657339</v>
+        <v>2.709803649431759</v>
       </c>
       <c r="F8" t="n">
-        <v>19.7618180239577</v>
+        <v>3.211295428893126</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.87507703616772</v>
+        <v>6.154700018377254</v>
       </c>
       <c r="D9" t="n">
-        <v>27.55449146690971</v>
+        <v>4.477604863372828</v>
       </c>
       <c r="E9" t="n">
-        <v>16.6757147657339</v>
+        <v>2.709803649431759</v>
       </c>
       <c r="F9" t="n">
-        <v>19.7618180239577</v>
+        <v>3.211295428893126</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>54.66574141176171</v>
+        <v>8.883182979411277</v>
       </c>
       <c r="D10" t="n">
-        <v>55.51551344265145</v>
+        <v>9.021270934430861</v>
       </c>
       <c r="E10" t="n">
-        <v>16.6757147657339</v>
+        <v>2.709803649431759</v>
       </c>
       <c r="F10" t="n">
-        <v>19.7618180239577</v>
+        <v>3.211295428893126</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
